--- a/data/trans_bre/IP43-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP43-Clase-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 6,33</t>
+          <t>-13,32; 5,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 4,91</t>
+          <t>-9,72; 5,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 38,13</t>
+          <t>-47,79; 33,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 56,78</t>
+          <t>-59,35; 56,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 9,24</t>
+          <t>-10,35; 8,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 4,49</t>
+          <t>-6,64; 4,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 61,01</t>
+          <t>-40,78; 62,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,4; 83,98</t>
+          <t>-62,48; 78,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 11,5</t>
+          <t>-10,3; 11,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 6,32</t>
+          <t>-13,01; 6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 56,58</t>
+          <t>-32,14; 57,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 62,12</t>
+          <t>-62,86; 57,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 4,72</t>
+          <t>-9,2; 4,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 8,36</t>
+          <t>-1,94; 8,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 24,72</t>
+          <t>-33,46; 23,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 86,16</t>
+          <t>-13,34; 90,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 11,27</t>
+          <t>-5,71; 11,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 12,82</t>
+          <t>-1,57; 11,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 49,5</t>
+          <t>-17,9; 49,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 133,23</t>
+          <t>-12,28; 130,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 12,68</t>
+          <t>-5,76; 12,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 1,72</t>
+          <t>-11,46; 2,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 235,87</t>
+          <t>-46,56; 246,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,81; 83,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,33</t>
+          <t>-3,21; 3,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,94</t>
+          <t>-1,99; 3,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 21,6</t>
+          <t>-13,18; 18,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 39,72</t>
+          <t>-15,48; 40,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
